--- a/public/templates/electricity-template.xlsx
+++ b/public/templates/electricity-template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Karthik\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Hackathon\ESGroww\ESGroww\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A1E72BA-DE1A-4070-8A59-0ED350077618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{505545E0-FB6A-4AFC-9556-D457C228A8B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{B49615E9-5A23-4E16-930E-0790818C4CC4}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Month</t>
   </si>
@@ -42,26 +42,56 @@
     <t>Year</t>
   </si>
   <si>
-    <t>electricityKwh</t>
-  </si>
-  <si>
-    <t>renewableKwh</t>
-  </si>
-  <si>
-    <t>cost</t>
-  </si>
-  <si>
-    <t>peak demand</t>
-  </si>
-  <si>
-    <t>power factor</t>
+    <t>⚡  Electricity Consumption Upload Template</t>
+  </si>
+  <si>
+    <t>kWh_Consumption</t>
+  </si>
+  <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>Meter_Reading</t>
+  </si>
+  <si>
+    <t>Peak_Demand</t>
+  </si>
+  <si>
+    <t>Power_Factor</t>
+  </si>
+  <si>
+    <t>Renewable_kWh</t>
+  </si>
+  <si>
+    <t>Enter month as number (1–12) or text (Jan–Dec / January–December)</t>
+  </si>
+  <si>
+    <t>4-digit calendar year of the data entry</t>
+  </si>
+  <si>
+    <t>Total electricity units consumed from the grid during the month. Found on your electricity bill.</t>
+  </si>
+  <si>
+    <t>Total electricity bill amount paid for the month, including all taxes and surcharges</t>
+  </si>
+  <si>
+    <t>Meter reading value recorded at the end of the billing period</t>
+  </si>
+  <si>
+    <t>Maximum demand (MD) recorded on your electricity bill – the highest power draw in the month</t>
+  </si>
+  <si>
+    <t>Power factor value from bill (0–1). Closer to 1 = more efficient. Usually printed on the bill.</t>
+  </si>
+  <si>
+    <t>Units from renewable sources only – solar rooftop, wind, green tariff, etc. Enter 0 if none.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -71,22 +101,63 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF1A5276"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF717D7E"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A5276"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF117A65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF5FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -94,21 +165,72 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAEB6BF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFAEB6BF"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFAEB6BF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAEB6BF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFAEB6BF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFAEB6BF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFAEB6BF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -423,75 +545,317 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2153FB47-0611-47AE-8364-C1FBCA2D7F86}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16.1796875" customWidth="1"/>
+    <col min="2" max="2" width="11.26953125" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="17.26953125" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="20.08984375" customWidth="1"/>
+    <col min="7" max="7" width="21.1796875" customWidth="1"/>
+    <col min="8" max="8" width="21.26953125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="E2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="F2" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
+      <c r="G2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="60" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/public/templates/electricity-template.xlsx
+++ b/public/templates/electricity-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Hackathon\ESGroww\ESGroww\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{505545E0-FB6A-4AFC-9556-D457C228A8B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16626728-9417-4B29-BED0-48E9D8DAF7B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{B49615E9-5A23-4E16-930E-0790818C4CC4}"/>
   </bookViews>
@@ -121,11 +121,11 @@
       <family val="2"/>
     </font>
     <font>
-      <i/>
       <sz val="10"/>
-      <color rgb="FF717D7E"/>
-      <name val="Arial"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -212,25 +212,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -559,298 +560,298 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="60" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
